--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123828083</v>
       </c>
       <c r="B2" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -774,6 +774,516 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123920907</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92271</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>458744</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6808797</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123920669</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>458872</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6808710</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123920589</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78524</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>458749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6808795</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123920662</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>458749</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6808795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123920300</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79406</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>458749</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6808795</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920907</v>
+        <v>123920662</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R3" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920662</v>
+        <v>123920907</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458749</v>
+        <v>458744</v>
       </c>
       <c r="R6" t="n">
-        <v>6808795</v>
+        <v>6808797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920589</v>
+        <v>123920907</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458749</v>
+        <v>458744</v>
       </c>
       <c r="R5" t="n">
-        <v>6808795</v>
+        <v>6808797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920907</v>
+        <v>123920589</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
+        <v>78524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R6" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920662</v>
+        <v>123920669</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458749</v>
+        <v>458872</v>
       </c>
       <c r="R3" t="n">
-        <v>6808795</v>
+        <v>6808710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920669</v>
+        <v>123920907</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458872</v>
+        <v>458744</v>
       </c>
       <c r="R4" t="n">
-        <v>6808710</v>
+        <v>6808797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920907</v>
+        <v>123920662</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R5" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920589</v>
+        <v>123920300</v>
       </c>
       <c r="B6" t="n">
-        <v>78524</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123920300</v>
+        <v>123920589</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>78524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920662</v>
+        <v>123920300</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920300</v>
+        <v>123920662</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920907</v>
+        <v>123920662</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R4" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920662</v>
+        <v>123920907</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458749</v>
+        <v>458744</v>
       </c>
       <c r="R6" t="n">
-        <v>6808795</v>
+        <v>6808797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920662</v>
+        <v>123920907</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458749</v>
+        <v>458744</v>
       </c>
       <c r="R3" t="n">
-        <v>6808795</v>
+        <v>6808797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920300</v>
+        <v>123920669</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458749</v>
+        <v>458872</v>
       </c>
       <c r="R4" t="n">
-        <v>6808795</v>
+        <v>6808710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920907</v>
+        <v>123920589</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R5" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920589</v>
+        <v>123920300</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123920669</v>
+        <v>123920662</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458872</v>
+        <v>458749</v>
       </c>
       <c r="R7" t="n">
-        <v>6808710</v>
+        <v>6808795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920907</v>
+        <v>123920662</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R3" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920669</v>
+        <v>123920907</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458872</v>
+        <v>458744</v>
       </c>
       <c r="R4" t="n">
-        <v>6808710</v>
+        <v>6808797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920589</v>
+        <v>123920300</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920300</v>
+        <v>123920589</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123920662</v>
+        <v>123920669</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458749</v>
+        <v>458872</v>
       </c>
       <c r="R7" t="n">
-        <v>6808795</v>
+        <v>6808710</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920662</v>
+        <v>123920907</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458749</v>
+        <v>458744</v>
       </c>
       <c r="R3" t="n">
-        <v>6808795</v>
+        <v>6808797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920907</v>
+        <v>123920300</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R4" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920300</v>
+        <v>123920589</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920589</v>
+        <v>123920662</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 46486-2023 artfynd.xlsx
+++ b/artfynd/A 46486-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123920907</v>
+        <v>123920662</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>458749</v>
       </c>
       <c r="R3" t="n">
-        <v>6808797</v>
+        <v>6808795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123920300</v>
+        <v>123920669</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458749</v>
+        <v>458872</v>
       </c>
       <c r="R4" t="n">
-        <v>6808795</v>
+        <v>6808710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123920589</v>
+        <v>123920300</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123920662</v>
+        <v>123920589</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123920669</v>
+        <v>123920907</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458872</v>
+        <v>458744</v>
       </c>
       <c r="R7" t="n">
-        <v>6808710</v>
+        <v>6808797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
